--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ARKANSAS_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ARKANSAS_2020.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Montecristo De Guerero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C29">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C54">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C94">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C112">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C157">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C162">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C171">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C423">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C436">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C442">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C478">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C493">
